--- a/templetes/温眼模板.xlsx
+++ b/templetes/温眼模板.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
     <t>一票通</t>
   </si>
@@ -71,38 +71,7 @@
     <t>商品名称</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-      </rPr>
-      <t>商品</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Serif CJK SC"/>
-        <charset val="134"/>
-      </rPr>
-      <t>规</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-      </rPr>
-      <t>格/型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Serif CJK SC"/>
-        <charset val="134"/>
-      </rPr>
-      <t>号</t>
-    </r>
+    <t>商品规格/型号</t>
   </si>
   <si>
     <t>生产企业</t>
@@ -139,6 +108,9 @@
   </si>
   <si>
     <t>金额合计（大写）：</t>
+  </si>
+  <si>
+    <t>amount_cht</t>
   </si>
   <si>
     <t>金额合计：</t>
@@ -167,7 +139,7 @@
     <numFmt numFmtId="179" formatCode="[DBNum2][$RMB]General;[Red][DBNum2][$RMB]General"/>
     <numFmt numFmtId="180" formatCode="0.00_);[Red]\(0.00\)"/>
   </numFmts>
-  <fonts count="33">
+  <fonts count="29">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -217,26 +189,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="10"/>
       <name val="宋体"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="等线"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
@@ -394,11 +350,6 @@
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Noto Serif CJK SC"/>
-      <charset val="134"/>
     </font>
   </fonts>
   <fills count="33">
@@ -760,133 +711,133 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="5" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -924,7 +875,7 @@
     <xf numFmtId="178" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -936,7 +887,7 @@
     <xf numFmtId="176" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -945,26 +896,26 @@
     <xf numFmtId="176" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="179" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="180" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -979,13 +930,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="12" fillId="0" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="9" fillId="0" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -1714,27 +1665,26 @@
       <c r="B9" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="C9" s="26" t="str">
-        <f>G9</f>
-        <v>amount</v>
+      <c r="C9" s="26" t="s">
+        <v>27</v>
       </c>
       <c r="D9" s="26"/>
       <c r="E9" s="27"/>
       <c r="F9" s="25" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G9" s="28" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H9" s="29"/>
       <c r="I9" s="25"/>
       <c r="J9" s="25"/>
       <c r="K9" s="21"/>
       <c r="L9" s="30" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M9" s="31" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" ht="23.25" spans="1:13">
